--- a/docs/manada/materiais/Painel-4-Indicadores-FQC.xlsx
+++ b/docs/manada/materiais/Painel-4-Indicadores-FQC.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Taxa de poupança = quanto sobrou ÷ entradas. Meta inicial: 10% ou mais.</t>
   </si>
   <si>
-    <t xml:space="preserve">Índice de endividamento = parcelas de dívidas ÷ entradas. Ideal: até 30%.</t>
+    <t xml:space="preserve">Índice de endividamento = parcelas de dívidas ÷ entradas. Saudável: até 10%. Atenção: de 10% a 20%. Alerta: acima de 20%.</t>
   </si>
   <si>
     <t xml:space="preserve">Meses de reserva = reserva ÷ gastos fixos. Meta: de 3 a 6 meses (6 a 12 para renda variável).</t>
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Índice de endividamento</t>
   </si>
   <si>
-    <t xml:space="preserve">Até 30% é saudável. Acima de 40%, renegociar vira prioridade.</t>
+    <t xml:space="preserve">Até 10% é saudável. Acima de 20%, renegociar vira prioridade. Rotativo ou cheque especial: trate como alerta.</t>
   </si>
   <si>
     <t xml:space="preserve">Meses de reserva</t>
@@ -972,11 +972,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="18002611"/>
-        <c:axId val="25553848"/>
+        <c:axId val="38135015"/>
+        <c:axId val="34162304"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="18002611"/>
+        <c:axId val="38135015"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1008,7 +1008,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25553848"/>
+        <c:crossAx val="34162304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1016,7 +1016,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="25553848"/>
+        <c:axId val="34162304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1058,7 +1058,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18002611"/>
+        <c:crossAx val="38135015"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1268,11 +1268,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="87417163"/>
-        <c:axId val="99230004"/>
+        <c:axId val="90818380"/>
+        <c:axId val="99097284"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="87417163"/>
+        <c:axId val="90818380"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1304,7 +1304,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99230004"/>
+        <c:crossAx val="99097284"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1312,7 +1312,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="99230004"/>
+        <c:axId val="99097284"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1354,7 +1354,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87417163"/>
+        <c:crossAx val="90818380"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1389,13 +1389,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>101160</xdr:rowOff>
+      <xdr:rowOff>7560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>966600</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>133560</xdr:rowOff>
+      <xdr:rowOff>40320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1419,13 +1419,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>101160</xdr:rowOff>
+      <xdr:rowOff>7920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>966600</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>133920</xdr:rowOff>
+      <xdr:rowOff>40320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1707,7 +1707,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="13" t="s">
         <v>24</v>
       </c>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="D7" s="15" t="str">
         <f aca="false">IFERROR(INDEX(Meses!$L$6:$L$17,MATCH(9.99E+307,Meses!$C$6:$C$17)),"")</f>
-        <v>Saudável</v>
+        <v>Atenção</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>25</v>
@@ -1890,7 +1890,7 @@
         <v>35</v>
       </c>
       <c r="C23" s="22" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1898,7 +1898,7 @@
         <v>36</v>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="L6" s="27" t="str">
         <f aca="false">IF(K6="","",IF(K6&lt;=Painel!$C$23,"Saudável",IF(K6&lt;=Painel!$C$24,"Atenção","Alerta")))</f>
-        <v>Saudável</v>
+        <v>Atenção</v>
       </c>
       <c r="M6" s="28" t="n">
         <f aca="false">IF(OR(N(C6)=0,N(D6)=0),"",G6/D6)</f>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="L8" s="27" t="str">
         <f aca="false">IF(K8="","",IF(K8&lt;=Painel!$C$23,"Saudável",IF(K8&lt;=Painel!$C$24,"Atenção","Alerta")))</f>
-        <v>Saudável</v>
+        <v>Atenção</v>
       </c>
       <c r="M8" s="28" t="n">
         <f aca="false">IF(OR(N(C8)=0,N(D8)=0),"",G8/D8)</f>
